--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Midcap 150 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Midcap 150 Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="384">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Midcap 150 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,24 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>BSE Ltd.</t>
+  </si>
+  <si>
+    <t>INE118H01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Suzlon Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE040H01021</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
     <t>MAX Healthcare Institute Ltd</t>
   </si>
   <si>
@@ -70,292 +88,409 @@
     <t>Healthcare Services</t>
   </si>
   <si>
-    <t>BSE Ltd.</t>
-  </si>
-  <si>
-    <t>INE118H01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Suzlon Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE040H01021</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>The Indian Hotels Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE053A01029</t>
+    <t>Persistent Systems Ltd.</t>
+  </si>
+  <si>
+    <t>INE262H01021</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>PB Fintech Ltd.</t>
+  </si>
+  <si>
+    <t>INE417T01026</t>
+  </si>
+  <si>
+    <t>Financial Technology (Fintech)</t>
+  </si>
+  <si>
+    <t>COFORGE Ltd.</t>
+  </si>
+  <si>
+    <t>INE591G01017</t>
+  </si>
+  <si>
+    <t>Dixon Technologies (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE935N01020</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd.</t>
+  </si>
+  <si>
+    <t>INE121J01017</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>The Federal Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE171A01029</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>IDFC First Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE092T01019</t>
+  </si>
+  <si>
+    <t>SRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE647A01010</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Yes Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE528G01035</t>
+  </si>
+  <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Solar Industries India Ltd.</t>
+  </si>
+  <si>
+    <t>INE343H01029</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE949L01017</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Fortis Healthcare Ltd.</t>
+  </si>
+  <si>
+    <t>INE061F01013</t>
+  </si>
+  <si>
+    <t>Sundaram Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE660A01013</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Godrej Properties Ltd.</t>
+  </si>
+  <si>
+    <t>INE484J01027</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Bharat Heavy Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE257A01026</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Tube Investments of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE974X01010</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE702C01027</t>
+  </si>
+  <si>
+    <t>Colgate - Palmolive (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE259A01022</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>One 97 Communications Ltd</t>
+  </si>
+  <si>
+    <t>INE982J01020</t>
+  </si>
+  <si>
+    <t>Polycab India Ltd.</t>
+  </si>
+  <si>
+    <t>INE455K01017</t>
+  </si>
+  <si>
+    <t>Gmr Airports Ltd.</t>
+  </si>
+  <si>
+    <t>INE776C01039</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Mphasis Ltd.</t>
+  </si>
+  <si>
+    <t>INE356A01018</t>
+  </si>
+  <si>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>Voltas Ltd.</t>
+  </si>
+  <si>
+    <t>INE226A01021</t>
+  </si>
+  <si>
+    <t>The Phoenix Mills Ltd.</t>
+  </si>
+  <si>
+    <t>INE211B01039</t>
+  </si>
+  <si>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd</t>
+  </si>
+  <si>
+    <t>INE634S01028</t>
+  </si>
+  <si>
+    <t>Ge Vernova T&amp;D India Ltd.</t>
+  </si>
+  <si>
+    <t>INE200A01026</t>
+  </si>
+  <si>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>NHPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE848E01016</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>SBI Cards &amp; Payment Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE018E01016</t>
+  </si>
+  <si>
+    <t>MRF Ltd.</t>
+  </si>
+  <si>
+    <t>INE883A01011</t>
+  </si>
+  <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Coromandel International Ltd.</t>
+  </si>
+  <si>
+    <t>INE169A01031</t>
+  </si>
+  <si>
+    <t>Supreme Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE195A01028</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE813H01021</t>
+  </si>
+  <si>
+    <t>Jubilant Foodworks Ltd.</t>
+  </si>
+  <si>
+    <t>INE797F01020</t>
   </si>
   <si>
     <t>Leisure Services</t>
   </si>
   <si>
-    <t>Persistent Systems Ltd.</t>
-  </si>
-  <si>
-    <t>INE262H01021</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Dixon Technologies (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE935N01020</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>PB Fintech Ltd.</t>
-  </si>
-  <si>
-    <t>INE417T01026</t>
-  </si>
-  <si>
-    <t>Financial Technology (Fintech)</t>
-  </si>
-  <si>
-    <t>COFORGE Ltd.</t>
-  </si>
-  <si>
-    <t>INE591G01017</t>
-  </si>
-  <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>The Federal Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE171A01029</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd.</t>
-  </si>
-  <si>
-    <t>INE121J01017</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>SRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE647A01010</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>CG Power and Industrial Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE067A01029</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>IDFC First Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE092T01019</t>
-  </si>
-  <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>Colgate - Palmolive (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE259A01022</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Yes Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE528G01035</t>
-  </si>
-  <si>
-    <t>Tube Investments of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE974X01010</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Marico Ltd.</t>
-  </si>
-  <si>
-    <t>INE196A01026</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd.</t>
-  </si>
-  <si>
-    <t>INE484J01027</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>AU Small Finance Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE949L01017</t>
-  </si>
-  <si>
-    <t>Fortis Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE061F01013</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Mphasis Ltd.</t>
-  </si>
-  <si>
-    <t>INE356A01018</t>
-  </si>
-  <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Sundaram Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE660A01013</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>The Phoenix Mills Ltd.</t>
-  </si>
-  <si>
-    <t>INE211B01039</t>
-  </si>
-  <si>
-    <t>UPL Ltd.</t>
-  </si>
-  <si>
-    <t>INE628A01036</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Polycab India Ltd.</t>
-  </si>
-  <si>
-    <t>INE455K01017</t>
-  </si>
-  <si>
-    <t>Voltas Ltd.</t>
-  </si>
-  <si>
-    <t>INE226A01021</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE813H01021</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>APL Apollo Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE702C01027</t>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Hitachi Energy India Ltd.</t>
+  </si>
+  <si>
+    <t>INE07Y701011</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd.</t>
+  </si>
+  <si>
+    <t>INE073K01018</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE414G01012</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Petronet LNG Ltd.</t>
+  </si>
+  <si>
+    <t>INE347G01014</t>
+  </si>
+  <si>
+    <t>Gas</t>
   </si>
   <si>
     <t>Rail Vikas Nigam Ltd.</t>
@@ -367,43 +502,25 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Jubilant Foodworks Ltd.</t>
-  </si>
-  <si>
-    <t>INE797F01020</t>
-  </si>
-  <si>
-    <t>One 97 Communications Ltd</t>
-  </si>
-  <si>
-    <t>INE982J01020</t>
-  </si>
-  <si>
-    <t>Gmr Airports Ltd.</t>
-  </si>
-  <si>
-    <t>INE776C01039</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Supreme Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE195A01028</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd</t>
-  </si>
-  <si>
-    <t>INE634S01028</t>
+    <t>JK Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE823G01014</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE335Y01020</t>
+  </si>
+  <si>
+    <t>Tata Elxsi Ltd.</t>
+  </si>
+  <si>
+    <t>INE670A01012</t>
   </si>
   <si>
     <t>KEI Industries Ltd.</t>
@@ -412,25 +529,91 @@
     <t>INE878B01027</t>
   </si>
   <si>
-    <t>Solar Industries India Ltd.</t>
-  </si>
-  <si>
-    <t>INE343H01029</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G01012</t>
-  </si>
-  <si>
-    <t>Petronet LNG Ltd.</t>
-  </si>
-  <si>
-    <t>INE347G01014</t>
-  </si>
-  <si>
-    <t>Gas</t>
+    <t>Glenmark Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE935A01035</t>
+  </si>
+  <si>
+    <t>KPIT Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE04I401011</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
+  </si>
+  <si>
+    <t>Container Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE111A01025</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Kalyan Jewellers India Ltd.</t>
+  </si>
+  <si>
+    <t>INE303R01014</t>
+  </si>
+  <si>
+    <t>Mazagon Dock Shipbuilders Ltd</t>
+  </si>
+  <si>
+    <t>INE249Z01020</t>
+  </si>
+  <si>
+    <t>Industrial Manufacturing</t>
+  </si>
+  <si>
+    <t>Jindal Stainless Ltd.</t>
+  </si>
+  <si>
+    <t>INE220G01021</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Oracle Financial Services Software Ltd.</t>
+  </si>
+  <si>
+    <t>INE881D01027</t>
+  </si>
+  <si>
+    <t>Blue Star Ltd.</t>
+  </si>
+  <si>
+    <t>INE472A01039</t>
+  </si>
+  <si>
+    <t>IPCA Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE571A01038</t>
+  </si>
+  <si>
+    <t>Balkrishna Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE787D01026</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
   </si>
   <si>
     <t>Vodafone Idea Ltd.</t>
@@ -439,118 +622,25 @@
     <t>INE669E01016</t>
   </si>
   <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>KPIT Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE04I401011</t>
-  </si>
-  <si>
-    <t>Oil India Ltd.</t>
-  </si>
-  <si>
-    <t>INE274J01014</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
-  </si>
-  <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Sona Blw Precision Forgings Ltd.</t>
-  </si>
-  <si>
-    <t>INE073K01018</t>
-  </si>
-  <si>
-    <t>Balkrishna Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE787D01026</t>
-  </si>
-  <si>
-    <t>Tata Elxsi Ltd.</t>
-  </si>
-  <si>
-    <t>INE670A01012</t>
-  </si>
-  <si>
-    <t>Container Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE111A01025</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Oracle Financial Services Software Ltd.</t>
-  </si>
-  <si>
-    <t>INE881D01027</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
-  </si>
-  <si>
-    <t>Jindal Stainless Ltd.</t>
-  </si>
-  <si>
-    <t>INE220G01021</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Coromandel International Ltd.</t>
-  </si>
-  <si>
-    <t>INE169A01031</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE823G01014</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>Adani total gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE399L01023</t>
+  </si>
+  <si>
+    <t>Steel Authority Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>Bharat Dynamics Ltd.</t>
+  </si>
+  <si>
+    <t>INE171Z01026</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
   </si>
   <si>
     <t>Patanjali Foods Ltd.</t>
@@ -559,36 +649,18 @@
     <t>INE619A01035</t>
   </si>
   <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
-  </si>
-  <si>
-    <t>IPCA Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE571A01038</t>
-  </si>
-  <si>
-    <t>Kalyan Jewellers India Ltd.</t>
-  </si>
-  <si>
-    <t>INE303R01014</t>
-  </si>
-  <si>
-    <t>Tata Communications Ltd.</t>
-  </si>
-  <si>
-    <t>INE151A01013</t>
-  </si>
-  <si>
     <t>Astral Ltd.</t>
   </si>
   <si>
     <t>INE006I01046</t>
   </si>
   <si>
+    <t>UNO Minda Ltd.</t>
+  </si>
+  <si>
+    <t>INE405E01023</t>
+  </si>
+  <si>
     <t>LIC Housing Finance Ltd.</t>
   </si>
   <si>
@@ -601,22 +673,85 @@
     <t>INE302A01020</t>
   </si>
   <si>
-    <t>UNO Minda Ltd.</t>
-  </si>
-  <si>
-    <t>INE405E01023</t>
-  </si>
-  <si>
     <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
   </si>
   <si>
     <t>INE774D01024</t>
   </si>
   <si>
-    <t>Delhivery Ltd.</t>
-  </si>
-  <si>
-    <t>INE148O01028</t>
+    <t>Lloyds Metals &amp; Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE281B01032</t>
+  </si>
+  <si>
+    <t>Schaeffler India Ltd.</t>
+  </si>
+  <si>
+    <t>INE513A01022</t>
+  </si>
+  <si>
+    <t>Hindustan Zinc Ltd.</t>
+  </si>
+  <si>
+    <t>INE267A01025</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Cochin Shipyard Ltd.</t>
+  </si>
+  <si>
+    <t>INE704P01025</t>
+  </si>
+  <si>
+    <t>Berger Paints India Ltd.</t>
+  </si>
+  <si>
+    <t>INE463A01038</t>
+  </si>
+  <si>
+    <t>National Aluminium Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE139A01034</t>
+  </si>
+  <si>
+    <t>Dalmia Bharat Ltd.</t>
+  </si>
+  <si>
+    <t>INE00R701025</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Aditya Birla Capital Ltd.</t>
+  </si>
+  <si>
+    <t>INE674K01013</t>
+  </si>
+  <si>
+    <t>Abbott India Ltd.</t>
+  </si>
+  <si>
+    <t>INE358A01014</t>
+  </si>
+  <si>
+    <t>Linde India Ltd.</t>
+  </si>
+  <si>
+    <t>INE473A01011</t>
+  </si>
+  <si>
+    <t>Apollo Tyres Ltd.</t>
+  </si>
+  <si>
+    <t>INE438A01022</t>
   </si>
   <si>
     <t>Biocon Ltd.</t>
@@ -625,6 +760,24 @@
     <t>INE376G01013</t>
   </si>
   <si>
+    <t>Bank Of India</t>
+  </si>
+  <si>
+    <t>INE084A01016</t>
+  </si>
+  <si>
+    <t>Gujarat Fluorochemicals Ltd.</t>
+  </si>
+  <si>
+    <t>INE09N301011</t>
+  </si>
+  <si>
+    <t>Indraprastha Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE203G01027</t>
+  </si>
+  <si>
     <t>United Breweries Ltd.</t>
   </si>
   <si>
@@ -634,37 +787,46 @@
     <t>Beverages</t>
   </si>
   <si>
+    <t>Bandhan Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
+  </si>
+  <si>
     <t>Deepak Nitrite Ltd.</t>
   </si>
   <si>
     <t>INE288B01029</t>
   </si>
   <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
-  </si>
-  <si>
-    <t>Tata Chemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE092A01019</t>
-  </si>
-  <si>
-    <t>Mazagon Dock Shipbuilders Ltd</t>
-  </si>
-  <si>
-    <t>INE249Z01020</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
-  </si>
-  <si>
-    <t>Lloyds Metals &amp; Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE281B01032</t>
+    <t>Bharti Hexacom Ltd.</t>
+  </si>
+  <si>
+    <t>INE343G01021</t>
+  </si>
+  <si>
+    <t>L&amp;T Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE498L01015</t>
+  </si>
+  <si>
+    <t>Apar Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE372A01015</t>
+  </si>
+  <si>
+    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE159A01016</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
   </si>
   <si>
     <t>Thermax Ltd.</t>
@@ -673,6 +835,54 @@
     <t>INE152A01029</t>
   </si>
   <si>
+    <t>Nippon Life India Asset Management Ltd</t>
+  </si>
+  <si>
+    <t>INE298J01013</t>
+  </si>
+  <si>
+    <t>CRISIL Ltd.</t>
+  </si>
+  <si>
+    <t>INE007A01025</t>
+  </si>
+  <si>
+    <t>General Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE481Y01014</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Housing &amp; Urban Development Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE031A01017</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE338I01027</t>
+  </si>
+  <si>
     <t>L&amp;T Technology Services Ltd.</t>
   </si>
   <si>
@@ -682,52 +892,10 @@
     <t>It - Services</t>
   </si>
   <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>Gujarat Fluorochemicals Ltd.</t>
-  </si>
-  <si>
-    <t>INE09N301011</t>
-  </si>
-  <si>
-    <t>Apollo Tyres Ltd.</t>
-  </si>
-  <si>
-    <t>INE438A01022</t>
-  </si>
-  <si>
-    <t>AIA Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE212H01026</t>
-  </si>
-  <si>
-    <t>Indraprastha Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE203G01027</t>
-  </si>
-  <si>
-    <t>Schaeffler India Ltd.</t>
-  </si>
-  <si>
-    <t>INE513A01022</t>
-  </si>
-  <si>
-    <t>Bank Of India</t>
-  </si>
-  <si>
-    <t>INE084A01016</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
+    <t>Tata Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE142M01025</t>
   </si>
   <si>
     <t>Indian Renewable Energy Development Agency Ltd</t>
@@ -736,106 +904,16 @@
     <t>INE202E01016</t>
   </si>
   <si>
-    <t>Abbott India Ltd.</t>
-  </si>
-  <si>
-    <t>INE358A01014</t>
-  </si>
-  <si>
-    <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
-  </si>
-  <si>
-    <t>INE179A01014</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Berger Paints India Ltd.</t>
-  </si>
-  <si>
-    <t>INE463A01038</t>
-  </si>
-  <si>
-    <t>Hitachi Energy India Ltd.</t>
-  </si>
-  <si>
-    <t>INE07Y701011</t>
-  </si>
-  <si>
-    <t>Hindustan Zinc Ltd.</t>
-  </si>
-  <si>
-    <t>INE267A01025</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Carborundum Universal Ltd.</t>
-  </si>
-  <si>
-    <t>INE120A01034</t>
-  </si>
-  <si>
-    <t>CRISIL Ltd.</t>
-  </si>
-  <si>
-    <t>INE007A01025</t>
-  </si>
-  <si>
-    <t>Linde India Ltd.</t>
-  </si>
-  <si>
-    <t>INE473A01011</t>
-  </si>
-  <si>
-    <t>Cochin Shipyard Ltd.</t>
-  </si>
-  <si>
-    <t>INE704P01025</t>
-  </si>
-  <si>
-    <t>Aditya Birla Capital Ltd.</t>
-  </si>
-  <si>
-    <t>INE674K01013</t>
-  </si>
-  <si>
-    <t>General Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE481Y01014</t>
-  </si>
-  <si>
-    <t>Bandhan Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE545U01014</t>
-  </si>
-  <si>
-    <t>Tata Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE142M01025</t>
-  </si>
-  <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
-    <t>Bharat Dynamics Ltd.</t>
-  </si>
-  <si>
-    <t>INE171Z01026</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
+    <t>Emami Ltd.</t>
+  </si>
+  <si>
+    <t>INE548C01032</t>
+  </si>
+  <si>
+    <t>K.P.R. Mill Ltd.</t>
+  </si>
+  <si>
+    <t>INE930H01031</t>
   </si>
   <si>
     <t>Escorts Kubota Ltd</t>
@@ -844,10 +922,157 @@
     <t>INE042A01014</t>
   </si>
   <si>
-    <t>L&amp;T Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE498L01015</t>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Ajanta Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE031B01049</t>
+  </si>
+  <si>
+    <t>IRB Infrastructure Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE821I01022</t>
+  </si>
+  <si>
+    <t>Global Health Ltd</t>
+  </si>
+  <si>
+    <t>INE474Q01031</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>Vishal Mega Mart Ltd.</t>
+  </si>
+  <si>
+    <t>INE01EA01019</t>
+  </si>
+  <si>
+    <t>Adani Wilmar Ltd</t>
+  </si>
+  <si>
+    <t>INE699H01024</t>
+  </si>
+  <si>
+    <t>Tata Investment Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE672A01018</t>
+  </si>
+  <si>
+    <t>Endurance Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE913H01037</t>
+  </si>
+  <si>
+    <t>Bank Of Maharashtra</t>
+  </si>
+  <si>
+    <t>INE457A01014</t>
+  </si>
+  <si>
+    <t>Honeywell Automation India Ltd.</t>
+  </si>
+  <si>
+    <t>INE671A01010</t>
+  </si>
+  <si>
+    <t>NTPC Green Energy Ltd</t>
+  </si>
+  <si>
+    <t>INE0ONG01011</t>
+  </si>
+  <si>
+    <t>3M India Ltd.</t>
+  </si>
+  <si>
+    <t>INE470A01017</t>
+  </si>
+  <si>
+    <t>Diversified</t>
+  </si>
+  <si>
+    <t>Aditya Birla Lifestyle Brands Ltd.</t>
+  </si>
+  <si>
+    <t>INE14LE01019</t>
+  </si>
+  <si>
+    <t>Gujarat Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE844O01030</t>
+  </si>
+  <si>
+    <t>JSW Infrastructure Ltd</t>
+  </si>
+  <si>
+    <t>INE880J01026</t>
+  </si>
+  <si>
+    <t>NLC India Ltd.</t>
+  </si>
+  <si>
+    <t>INE589A01014</t>
+  </si>
+  <si>
+    <t>WAAREE Energies Ltd</t>
+  </si>
+  <si>
+    <t>INE377N01017</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE233A01035</t>
+  </si>
+  <si>
+    <t>Premier Energies Ltd.</t>
+  </si>
+  <si>
+    <t>INE0BS701011</t>
+  </si>
+  <si>
+    <t>SJVN Ltd.</t>
+  </si>
+  <si>
+    <t>INE002L01015</t>
+  </si>
+  <si>
+    <t>Sun TV Network Ltd.</t>
+  </si>
+  <si>
+    <t>INE424H01027</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Ola Electric Mobility Ltd.</t>
+  </si>
+  <si>
+    <t>INE0LXG01040</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>The New India Assurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE470Y01017</t>
   </si>
   <si>
     <t>Aditya Birla Fashion and Retail Ltd.</t>
@@ -856,222 +1081,6 @@
     <t>INE647O01011</t>
   </si>
   <si>
-    <t>Emami Ltd.</t>
-  </si>
-  <si>
-    <t>INE548C01032</t>
-  </si>
-  <si>
-    <t>Sundram Fasteners Ltd.</t>
-  </si>
-  <si>
-    <t>INE387A01021</t>
-  </si>
-  <si>
-    <t>Housing &amp; Urban Development Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE031A01017</t>
-  </si>
-  <si>
-    <t>IRB Infrastructure Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE821I01022</t>
-  </si>
-  <si>
-    <t>Ajanta Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE031B01049</t>
-  </si>
-  <si>
-    <t>Timken India Ltd.</t>
-  </si>
-  <si>
-    <t>INE325A01013</t>
-  </si>
-  <si>
-    <t>Bharti Hexacom Ltd.</t>
-  </si>
-  <si>
-    <t>INE343G01021</t>
-  </si>
-  <si>
-    <t>Nippon Life India Asset Management Ltd</t>
-  </si>
-  <si>
-    <t>INE298J01013</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>SKF India Ltd.</t>
-  </si>
-  <si>
-    <t>INE640A01023</t>
-  </si>
-  <si>
-    <t>K.P.R. Mill Ltd.</t>
-  </si>
-  <si>
-    <t>INE930H01031</t>
-  </si>
-  <si>
-    <t>Poonawalla Fincorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE511C01022</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Ltd.</t>
-  </si>
-  <si>
-    <t>INE536A01023</t>
-  </si>
-  <si>
-    <t>Honeywell Automation India Ltd.</t>
-  </si>
-  <si>
-    <t>INE671A01010</t>
-  </si>
-  <si>
-    <t>Global Health Ltd</t>
-  </si>
-  <si>
-    <t>INE474Q01031</t>
-  </si>
-  <si>
-    <t>3M India Ltd.</t>
-  </si>
-  <si>
-    <t>INE470A01017</t>
-  </si>
-  <si>
-    <t>Diversified</t>
-  </si>
-  <si>
-    <t>Gujarat Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE844O01030</t>
-  </si>
-  <si>
-    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE159A01016</t>
-  </si>
-  <si>
-    <t>Bank Of Maharashtra</t>
-  </si>
-  <si>
-    <t>INE457A01014</t>
-  </si>
-  <si>
-    <t>Tata Investment Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE672A01018</t>
-  </si>
-  <si>
-    <t>JSW Infrastructure Ltd</t>
-  </si>
-  <si>
-    <t>INE880J01026</t>
-  </si>
-  <si>
-    <t>NLC India Ltd.</t>
-  </si>
-  <si>
-    <t>INE589A01014</t>
-  </si>
-  <si>
-    <t>Endurance Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE913H01037</t>
-  </si>
-  <si>
-    <t>SJVN Ltd.</t>
-  </si>
-  <si>
-    <t>INE002L01015</t>
-  </si>
-  <si>
-    <t>ZF Commercial Vehicle Control Systems India Ltd</t>
-  </si>
-  <si>
-    <t>INE342J01019</t>
-  </si>
-  <si>
-    <t>Bayer Cropscience Ltd.</t>
-  </si>
-  <si>
-    <t>INE462A01022</t>
-  </si>
-  <si>
-    <t>The Fertilisers and Chemicals.</t>
-  </si>
-  <si>
-    <t>INE188A01015</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE233A01035</t>
-  </si>
-  <si>
-    <t>Sun TV Network Ltd.</t>
-  </si>
-  <si>
-    <t>INE424H01027</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>IDBI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE008A01015</t>
-  </si>
-  <si>
-    <t>Metro Brands Ltd.</t>
-  </si>
-  <si>
-    <t>INE317I01021</t>
-  </si>
-  <si>
-    <t>The New India Assurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE470Y01017</t>
-  </si>
-  <si>
-    <t>Adani Wilmar Ltd</t>
-  </si>
-  <si>
-    <t>INE699H01024</t>
-  </si>
-  <si>
-    <t>Indian Overseas Bank</t>
-  </si>
-  <si>
-    <t>INE565A01014</t>
-  </si>
-  <si>
     <t>Mangalore Refinery and Petrochemicals Ltd.</t>
   </si>
   <si>
@@ -1132,16 +1141,10 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
-    <t>KEI Industries Ltd</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd</t>
-  </si>
-  <si>
-    <t>Page Industries Limited</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd</t>
+    <t>FSN E-COMMERCE VENTURES LTD</t>
+  </si>
+  <si>
+    <t>L&amp;T Finance Ltd (Old-L&amp;T Finance Holdings Ltd)</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
@@ -1153,7 +1156,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1163,9 +1166,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Midcap 150 TRI</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1391,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1484,9 +1484,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1608,7 +1605,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="666750" y="40081200"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1647,7 +1644,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="666750" y="42938700"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:ext cx="3686175" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1980,19 +1977,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J222"/>
+  <dimension ref="B1:J221"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.571428571428573" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="50.285714285714285" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="55.285714285714285" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="50.285714285714285" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -2080,10 +2077,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>61304.009999999995</v>
+        <v>73072.89000000006</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9991732048488002</v>
+        <v>0.9986958455657</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -2117,10 +2114,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>61304.009999999995</v>
+        <v>73072.89000000006</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9991732048488002</v>
+        <v>0.9986958455657</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -2143,13 +2140,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>141714</v>
+        <v>85395</v>
       </c>
       <c r="G8" s="15">
-        <v>1503.94</v>
+        <v>2283.46</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0245122064561</v>
+        <v>0.0312083183726</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -2172,13 +2169,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>25869</v>
+        <v>2489672</v>
       </c>
       <c r="G9" s="15">
-        <v>1372.60</v>
+        <v>1779.62</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0223715404748</v>
+        <v>0.0243222773958</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -2201,13 +2198,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>2253113</v>
+        <v>155880</v>
       </c>
       <c r="G10" s="15">
-        <v>1310.64</v>
+        <v>1753.96</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0213616755121</v>
+        <v>0.0239715791355</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -2230,13 +2227,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>167874</v>
+        <v>22329</v>
       </c>
       <c r="G11" s="15">
-        <v>1283.73</v>
+        <v>1258.91</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0209230785762</v>
+        <v>0.0172056721302</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -2259,13 +2256,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>20114</v>
+        <v>69405</v>
       </c>
       <c r="G12" s="15">
-        <v>1213.4</v>
+        <v>1222.64</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0197767938308</v>
+        <v>0.0167099657428</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -2285,16 +2282,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F13" s="14">
-        <v>7268</v>
+        <v>13965</v>
       </c>
       <c r="G13" s="15">
-        <v>1089.18</v>
+        <v>1194.08</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0177521743074</v>
+        <v>0.0163196328389</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -2305,25 +2302,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F14" s="14">
-        <v>63052</v>
+        <v>8081</v>
       </c>
       <c r="G14" s="15">
-        <v>1088.78</v>
+        <v>1187.26</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0177456548435</v>
+        <v>0.0162264230909</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -2334,25 +2331,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F15" s="14">
-        <v>12693</v>
+        <v>277214</v>
       </c>
       <c r="G15" s="15">
-        <v>1048.93</v>
+        <v>1064.92</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0170961532495</v>
+        <v>0.0145543878156</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -2375,13 +2372,13 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>46022</v>
+        <v>514254</v>
       </c>
       <c r="G16" s="15">
-        <v>957.46</v>
+        <v>1039.1</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0156053148353</v>
+        <v>0.0142015028163</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -2401,16 +2398,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>467289</v>
+        <v>21271</v>
       </c>
       <c r="G17" s="15">
-        <v>874.81</v>
+        <v>1017.39</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0142582306009</v>
+        <v>0.013904789674</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2421,25 +2418,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" s="14">
-        <v>237006</v>
+        <v>50654</v>
       </c>
       <c r="G18" s="15">
-        <v>822.88</v>
+        <v>991.65</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0134118411962</v>
+        <v>0.0135529980443</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2450,25 +2447,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="F19" s="14">
-        <v>27674</v>
+        <v>28370</v>
       </c>
       <c r="G19" s="15">
-        <v>777.60</v>
+        <v>927.16</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0126738378793</v>
+        <v>0.0126716055733</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2479,25 +2476,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>51</v>
-      </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>122099</v>
+        <v>1300420</v>
       </c>
       <c r="G20" s="15">
-        <v>775.15</v>
+        <v>883.90</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0126339061628</v>
+        <v>0.0120803660277</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2508,25 +2505,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F21" s="14">
-        <v>25843</v>
+        <v>30426</v>
       </c>
       <c r="G21" s="15">
-        <v>753.08</v>
+        <v>870.49</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0122741947405</v>
+        <v>0.0118970899688</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2537,25 +2534,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F22" s="14">
-        <v>1181907</v>
+        <v>3954700</v>
       </c>
       <c r="G22" s="15">
-        <v>747.44</v>
+        <v>849.47</v>
       </c>
       <c r="H22" s="16">
-        <v>0.012182270299</v>
+        <v>0.0116098071383</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2566,25 +2563,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F23" s="14">
-        <v>19314</v>
+        <v>201476</v>
       </c>
       <c r="G23" s="15">
-        <v>747.43</v>
+        <v>828.17</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0121821073124</v>
+        <v>0.0113186975146</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2604,16 +2601,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F24" s="14">
-        <v>25259</v>
+        <v>5101</v>
       </c>
       <c r="G24" s="15">
-        <v>712.70</v>
+        <v>821.47</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0116160548567</v>
+        <v>0.0112271278207</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2624,25 +2621,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F25" s="14">
-        <v>3595526</v>
+        <v>117738</v>
       </c>
       <c r="G25" s="15">
-        <v>691.42</v>
+        <v>815.98</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0112692193757</v>
+        <v>0.0111520953402</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2653,25 +2650,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F26" s="14">
-        <v>20341</v>
+        <v>54105</v>
       </c>
       <c r="G26" s="15">
-        <v>675.75</v>
+        <v>813.04</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0110138193762</v>
+        <v>0.0111119140119</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2682,25 +2679,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="F27" s="14">
-        <v>100615</v>
+        <v>110690</v>
       </c>
       <c r="G27" s="15">
-        <v>674.77</v>
+        <v>793.04</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0109978466896</v>
+        <v>0.0108385716422</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2711,25 +2708,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F28" s="14">
-        <v>28761</v>
+        <v>109294</v>
       </c>
       <c r="G28" s="15">
-        <v>669.97</v>
+        <v>771.94</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0109196131225</v>
+        <v>0.0105501954422</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2740,25 +2737,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="F29" s="14">
-        <v>183186</v>
+        <v>14430</v>
       </c>
       <c r="G29" s="15">
-        <v>656.26</v>
+        <v>741.20</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0106961584963</v>
+        <v>0.01013006822</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2769,25 +2766,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="F30" s="14">
-        <v>106976</v>
+        <v>31627</v>
       </c>
       <c r="G30" s="15">
-        <v>642.87</v>
+        <v>709.65</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0104779194412</v>
+        <v>0.0096988706319</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2798,25 +2795,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F31" s="14">
-        <v>99360</v>
+        <v>300012</v>
       </c>
       <c r="G31" s="15">
-        <v>636.10</v>
+        <v>708.12</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0103675775142</v>
+        <v>0.0096779599406</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2836,16 +2833,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F32" s="14">
-        <v>53327</v>
+        <v>269591</v>
       </c>
       <c r="G32" s="15">
-        <v>624.94</v>
+        <v>700.48</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0101856844706</v>
+        <v>0.0095735431554</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2865,16 +2862,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="F33" s="14">
-        <v>21573</v>
+        <v>55924</v>
       </c>
       <c r="G33" s="15">
-        <v>618.7</v>
+        <v>693.96</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0100839808333</v>
+        <v>0.0094844335429</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2885,25 +2882,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F34" s="14">
-        <v>49911</v>
+        <v>22550</v>
       </c>
       <c r="G34" s="15">
-        <v>610.94</v>
+        <v>690.50</v>
       </c>
       <c r="H34" s="16">
-        <v>0.009957503233</v>
+        <v>0.0094371453129</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2914,25 +2911,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F35" s="14">
-        <v>13112</v>
+        <v>37987</v>
       </c>
       <c r="G35" s="15">
-        <v>605.38</v>
+        <v>688.21</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0098668826844</v>
+        <v>0.0094058476116</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2955,13 +2952,13 @@
         <v>91</v>
       </c>
       <c r="F36" s="14">
-        <v>273173</v>
+        <v>27628</v>
       </c>
       <c r="G36" s="15">
-        <v>592.32</v>
+        <v>678.52</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0096540221871</v>
+        <v>0.0092734132335</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2981,16 +2978,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F37" s="14">
-        <v>35549</v>
+        <v>58656</v>
       </c>
       <c r="G37" s="15">
-        <v>583.64</v>
+        <v>673.25</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0095125498198</v>
+        <v>0.0092013875191</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -3013,13 +3010,13 @@
         <v>96</v>
       </c>
       <c r="F38" s="14">
-        <v>96493</v>
+        <v>106146</v>
       </c>
       <c r="G38" s="15">
-        <v>582.58</v>
+        <v>666.49</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0094952732404</v>
+        <v>0.0091089977981</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -3039,16 +3036,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="F39" s="14">
-        <v>9579</v>
+        <v>16982</v>
       </c>
       <c r="G39" s="15">
-        <v>578.38</v>
+        <v>649.34</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0094268188691</v>
+        <v>0.0088746067161</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -3068,16 +3065,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F40" s="14">
-        <v>43546</v>
+        <v>71393</v>
       </c>
       <c r="G40" s="15">
-        <v>549.05</v>
+        <v>635.72</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0089487791765</v>
+        <v>0.0086884605624</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -3097,16 +3094,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="F41" s="14">
-        <v>49183</v>
+        <v>10569</v>
       </c>
       <c r="G41" s="15">
-        <v>548.76</v>
+        <v>633.19</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0089440525651</v>
+        <v>0.0086538827526</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -3117,25 +3114,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="D42" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="F42" s="14">
-        <v>15471</v>
+        <v>752236</v>
       </c>
       <c r="G42" s="15">
-        <v>538.97</v>
+        <v>632.48</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0087844886855</v>
+        <v>0.0086441790985</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -3155,16 +3152,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="F43" s="14">
-        <v>36264</v>
+        <v>23833</v>
       </c>
       <c r="G43" s="15">
-        <v>530.71</v>
+        <v>609.84</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0086498617553</v>
+        <v>0.008334755536</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -3175,25 +3172,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="D44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>111</v>
-      </c>
       <c r="F44" s="14">
-        <v>1185</v>
+        <v>1314</v>
       </c>
       <c r="G44" s="15">
-        <v>529.97</v>
+        <v>609.43</v>
       </c>
       <c r="H44" s="16">
-        <v>0.008637800747</v>
+        <v>0.0083291520174</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -3204,25 +3201,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F45" s="14">
-        <v>34519</v>
+        <v>47738</v>
       </c>
       <c r="G45" s="15">
-        <v>521.08</v>
+        <v>602.84</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0084929056612</v>
+        <v>0.0082390857066</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -3233,25 +3230,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F46" s="14">
-        <v>108269</v>
+        <v>39105</v>
       </c>
       <c r="G46" s="15">
-        <v>515.69</v>
+        <v>601.08</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0084050558848</v>
+        <v>0.0082150315781</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -3262,10 +3259,10 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
@@ -3274,13 +3271,13 @@
         <v>40</v>
       </c>
       <c r="F47" s="14">
-        <v>10121</v>
+        <v>405279</v>
       </c>
       <c r="G47" s="15">
-        <v>512.43</v>
+        <v>594.91</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0083519222537</v>
+        <v>0.0081307054571</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -3291,25 +3288,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F48" s="14">
-        <v>72786</v>
+        <v>23675</v>
       </c>
       <c r="G48" s="15">
-        <v>512.34</v>
+        <v>584.23</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0083504553743</v>
+        <v>0.0079847406317</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -3320,25 +3317,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F49" s="14">
-        <v>64784</v>
+        <v>25991</v>
       </c>
       <c r="G49" s="15">
-        <v>502.56</v>
+        <v>582.56</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0081910544813</v>
+        <v>0.0079619165438</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -3349,25 +3346,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>125</v>
-      </c>
       <c r="F50" s="14">
-        <v>683903</v>
+        <v>285845</v>
       </c>
       <c r="G50" s="15">
-        <v>496.99</v>
+        <v>581.01</v>
       </c>
       <c r="H50" s="16">
-        <v>0.008100270946</v>
+        <v>0.0079407325101</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -3378,25 +3375,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F51" s="14">
-        <v>12312</v>
+        <v>663633</v>
       </c>
       <c r="G51" s="15">
-        <v>488.64</v>
+        <v>580.08</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0079641771365</v>
+        <v>0.00792802209</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -3407,25 +3404,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F52" s="14">
-        <v>19809</v>
+        <v>62815</v>
       </c>
       <c r="G52" s="15">
-        <v>482.43</v>
+        <v>578.56</v>
       </c>
       <c r="H52" s="16">
-        <v>0.007862962459</v>
+        <v>0.0079072480699</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3436,25 +3433,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F53" s="14">
-        <v>11741</v>
+        <v>415</v>
       </c>
       <c r="G53" s="15">
-        <v>472.41</v>
+        <v>576.29</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0076996498876</v>
+        <v>0.0078762237109</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3465,25 +3462,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F54" s="14">
-        <v>4631</v>
+        <v>11141</v>
       </c>
       <c r="G54" s="15">
-        <v>472.11</v>
+        <v>568.02</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0076947602896</v>
+        <v>0.007763196641</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3494,25 +3491,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F55" s="14">
-        <v>20432</v>
+        <v>24758</v>
       </c>
       <c r="G55" s="15">
-        <v>461.52</v>
+        <v>566.81</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0075221574821</v>
+        <v>0.0077466594277</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3523,25 +3520,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F56" s="14">
-        <v>142940</v>
+        <v>13551</v>
       </c>
       <c r="G56" s="15">
-        <v>451.98</v>
+        <v>561.85</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0073666682673</v>
+        <v>0.00767887052</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3552,25 +3549,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="F57" s="14">
-        <v>4951028</v>
+        <v>39897</v>
       </c>
       <c r="G57" s="15">
-        <v>448.07</v>
+        <v>548.18</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0073029405074</v>
+        <v>0.0074920410103</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3581,25 +3578,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="F58" s="14">
-        <v>57091</v>
+        <v>79814</v>
       </c>
       <c r="G58" s="15">
-        <v>444.28</v>
+        <v>523.22</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0072411685867</v>
+        <v>0.007150909733</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3610,25 +3607,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>144</v>
-      </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="F59" s="14">
-        <v>259760</v>
+        <v>35375</v>
       </c>
       <c r="G59" s="15">
-        <v>438.73</v>
+        <v>518.81</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0071507110247</v>
+        <v>0.0070906377405</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3639,25 +3636,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="F60" s="14">
-        <v>31083</v>
+        <v>724940</v>
       </c>
       <c r="G60" s="15">
-        <v>438.02</v>
+        <v>515.94</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0071391389762</v>
+        <v>0.0070514131104</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3668,25 +3665,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F61" s="14">
-        <v>103992</v>
+        <v>2657</v>
       </c>
       <c r="G61" s="15">
-        <v>437.23</v>
+        <v>512.75</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0071262630349</v>
+        <v>0.0070078150024</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3697,25 +3694,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F62" s="14">
-        <v>32151</v>
+        <v>94097</v>
       </c>
       <c r="G62" s="15">
-        <v>437.09</v>
+        <v>511.84</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0071239812226</v>
+        <v>0.0069953779246</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3726,25 +3723,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F63" s="14">
-        <v>384</v>
+        <v>22484</v>
       </c>
       <c r="G63" s="15">
-        <v>436.35</v>
+        <v>498.11</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0071119202143</v>
+        <v>0.0068077283878</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3755,25 +3752,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>157</v>
-      </c>
       <c r="F64" s="14">
-        <v>659092</v>
+        <v>114390</v>
       </c>
       <c r="G64" s="15">
-        <v>435.66</v>
+        <v>488.22</v>
       </c>
       <c r="H64" s="16">
-        <v>0.007100674139</v>
+        <v>0.006672560586</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3784,25 +3781,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F65" s="14">
-        <v>85437</v>
+        <v>157200</v>
       </c>
       <c r="G65" s="15">
-        <v>430.86</v>
+        <v>483.08</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0070224405719</v>
+        <v>0.006602311597</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3813,25 +3810,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="D66" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F66" s="14">
-        <v>15314</v>
+        <v>119055</v>
       </c>
       <c r="G66" s="15">
-        <v>424.39</v>
+        <v>482.83</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0069169882428</v>
+        <v>0.0065988948174</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3851,16 +3848,16 @@
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="F67" s="14">
-        <v>6596</v>
+        <v>8767</v>
       </c>
       <c r="G67" s="15">
-        <v>417.92</v>
+        <v>481.97</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0068115359137</v>
+        <v>0.0065871410955</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3871,25 +3868,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F68" s="14">
-        <v>52552</v>
+        <v>63263</v>
       </c>
       <c r="G68" s="15">
-        <v>409.96</v>
+        <v>478.27</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0066817985815</v>
+        <v>0.0065365727571</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3909,16 +3906,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F69" s="14">
-        <v>4486</v>
+        <v>7263</v>
       </c>
       <c r="G69" s="15">
-        <v>409.22</v>
+        <v>467.70</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0066697375733</v>
+        <v>0.0063921113148</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3938,16 +3935,16 @@
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F70" s="14">
-        <v>22429</v>
+        <v>12918</v>
       </c>
       <c r="G70" s="15">
-        <v>406.56</v>
+        <v>466.37</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0066263831381</v>
+        <v>0.0063739340472</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3967,16 +3964,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="F71" s="14">
-        <v>62203</v>
+        <v>31575</v>
       </c>
       <c r="G71" s="15">
-        <v>406.37</v>
+        <v>460.08</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0066232863928</v>
+        <v>0.0062879678719</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3987,25 +3984,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>175</v>
-      </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="F72" s="14">
-        <v>22416</v>
+        <v>34232</v>
       </c>
       <c r="G72" s="15">
-        <v>405.63</v>
+        <v>457.96</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0066112253845</v>
+        <v>0.0062589935807</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -4016,25 +4013,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>177</v>
-      </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="F73" s="14">
-        <v>7968</v>
+        <v>74112</v>
       </c>
       <c r="G73" s="15">
-        <v>385.24</v>
+        <v>456.97</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0062788957107</v>
+        <v>0.0062454631334</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -4045,25 +4042,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="F74" s="14">
-        <v>20916</v>
+        <v>57809</v>
       </c>
       <c r="G74" s="15">
-        <v>381.63</v>
+        <v>453.45</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0062200575487</v>
+        <v>0.0061973548764</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -4074,25 +4071,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>182</v>
-      </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F75" s="14">
-        <v>67372</v>
+        <v>80548</v>
       </c>
       <c r="G75" s="15">
-        <v>374.42</v>
+        <v>451.39</v>
       </c>
       <c r="H75" s="16">
-        <v>0.0061025442114</v>
+        <v>0.0061692006123</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -4103,25 +4100,25 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F76" s="14">
-        <v>25882</v>
+        <v>12860</v>
       </c>
       <c r="G76" s="15">
-        <v>373.55</v>
+        <v>447.30</v>
       </c>
       <c r="H76" s="16">
-        <v>0.0060883643773</v>
+        <v>0.0061133020977</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -4141,16 +4138,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="F77" s="14">
-        <v>73127</v>
+        <v>67974</v>
       </c>
       <c r="G77" s="15">
-        <v>367.90</v>
+        <v>438.26</v>
       </c>
       <c r="H77" s="16">
-        <v>0.0059962769493</v>
+        <v>0.0059897513466</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -4161,25 +4158,25 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F78" s="14">
-        <v>22382</v>
+        <v>24679</v>
       </c>
       <c r="G78" s="15">
-        <v>365.50</v>
+        <v>430.97</v>
       </c>
       <c r="H78" s="16">
-        <v>0.0059571601657</v>
+        <v>0.0058901180529</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -4190,25 +4187,25 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F79" s="14">
-        <v>23562</v>
+        <v>4953</v>
       </c>
       <c r="G79" s="15">
-        <v>355.15</v>
+        <v>419.15</v>
       </c>
       <c r="H79" s="16">
-        <v>0.0057884690366</v>
+        <v>0.0057285727124</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -4219,25 +4216,25 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="F80" s="14">
-        <v>57335</v>
+        <v>27209</v>
       </c>
       <c r="G80" s="15">
-        <v>342.92</v>
+        <v>416.92</v>
       </c>
       <c r="H80" s="16">
-        <v>0.0055891364269</v>
+        <v>0.0056980950382</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -4248,25 +4245,25 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F81" s="14">
-        <v>86779</v>
+        <v>29143</v>
       </c>
       <c r="G81" s="15">
-        <v>324.99</v>
+        <v>415.23</v>
       </c>
       <c r="H81" s="16">
-        <v>0.0052969014563</v>
+        <v>0.0056749976079</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -4277,25 +4274,25 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F82" s="14">
-        <v>34080</v>
+        <v>16791</v>
       </c>
       <c r="G82" s="15">
-        <v>322.26</v>
+        <v>415.11</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0052524061149</v>
+        <v>0.0056733575537</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -4306,25 +4303,25 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F83" s="14">
-        <v>112831</v>
+        <v>24626</v>
       </c>
       <c r="G83" s="15">
-        <v>321.51</v>
+        <v>412.78</v>
       </c>
       <c r="H83" s="16">
-        <v>0.0052401821201</v>
+        <v>0.0056415131676</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -4335,25 +4332,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F84" s="14">
-        <v>97194</v>
+        <v>5791061</v>
       </c>
       <c r="G84" s="15">
-        <v>312.04</v>
+        <v>400.74</v>
       </c>
       <c r="H84" s="16">
-        <v>0.0050858338115</v>
+        <v>0.0054769610611</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -4364,25 +4361,25 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="F85" s="14">
-        <v>85834</v>
+        <v>58175</v>
       </c>
       <c r="G85" s="15">
-        <v>311.19</v>
+        <v>397.77</v>
       </c>
       <c r="H85" s="16">
-        <v>0.0050719799507</v>
+        <v>0.0054363697192</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -4393,25 +4390,25 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F86" s="14">
-        <v>14343</v>
+        <v>303208</v>
       </c>
       <c r="G86" s="15">
-        <v>307.80</v>
+        <v>391.68</v>
       </c>
       <c r="H86" s="16">
-        <v>0.0050167274939</v>
+        <v>0.0053531369676</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -4431,16 +4428,16 @@
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="F87" s="14">
-        <v>13094</v>
+        <v>19319</v>
       </c>
       <c r="G87" s="15">
-        <v>304.51</v>
+        <v>389.37</v>
       </c>
       <c r="H87" s="16">
-        <v>0.0049631049031</v>
+        <v>0.0053215659239</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4451,25 +4448,25 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="F88" s="14">
-        <v>275664</v>
+        <v>23232</v>
       </c>
       <c r="G88" s="15">
-        <v>296.15</v>
+        <v>388.28</v>
       </c>
       <c r="H88" s="16">
-        <v>0.0048268481069</v>
+        <v>0.0053066687648</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4480,25 +4477,25 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F89" s="14">
-        <v>29852</v>
+        <v>25833</v>
       </c>
       <c r="G89" s="15">
-        <v>294.37</v>
+        <v>387</v>
       </c>
       <c r="H89" s="16">
-        <v>0.0047978364924</v>
+        <v>0.0052891748531</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4509,25 +4506,25 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="F90" s="14">
-        <v>11687</v>
+        <v>37492</v>
       </c>
       <c r="G90" s="15">
-        <v>292</v>
+        <v>377.41</v>
       </c>
       <c r="H90" s="16">
-        <v>0.0047592086687</v>
+        <v>0.0051581071869</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>13</v>
@@ -4547,16 +4544,16 @@
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="F91" s="14">
-        <v>23133</v>
+        <v>63059</v>
       </c>
       <c r="G91" s="15">
-        <v>286.64</v>
+        <v>376.12</v>
       </c>
       <c r="H91" s="16">
-        <v>0.004671847852</v>
+        <v>0.005140476604</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>13</v>
@@ -4576,16 +4573,16 @@
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="F92" s="14">
-        <v>7369</v>
+        <v>95443</v>
       </c>
       <c r="G92" s="15">
-        <v>284.71</v>
+        <v>369.22</v>
       </c>
       <c r="H92" s="16">
-        <v>0.0046403914385</v>
+        <v>0.0050461734865</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>13</v>
@@ -4605,16 +4602,16 @@
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="F93" s="14">
-        <v>5220</v>
+        <v>139540</v>
       </c>
       <c r="G93" s="15">
-        <v>284.46</v>
+        <v>364.34</v>
       </c>
       <c r="H93" s="16">
-        <v>0.0046363167736</v>
+        <v>0.0049794779483</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>13</v>
@@ -4625,25 +4622,25 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C94" s="13" t="s">
-        <v>223</v>
-      </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="F94" s="14">
-        <v>15228</v>
+        <v>25490</v>
       </c>
       <c r="G94" s="15">
-        <v>284.21</v>
+        <v>355.10</v>
       </c>
       <c r="H94" s="16">
-        <v>0.0046322421086</v>
+        <v>0.0048531937735</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>13</v>
@@ -4654,25 +4651,25 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C95" s="13" t="s">
-        <v>225</v>
-      </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F95" s="14">
-        <v>7772</v>
+        <v>8434</v>
       </c>
       <c r="G95" s="15">
-        <v>278.05</v>
+        <v>353.27</v>
       </c>
       <c r="H95" s="16">
-        <v>0.0045318423641</v>
+        <v>0.0048281829467</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>13</v>
@@ -4683,25 +4680,25 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="D96" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F96" s="14">
-        <v>63458</v>
+        <v>76905</v>
       </c>
       <c r="G96" s="15">
-        <v>277.50</v>
+        <v>352.38</v>
       </c>
       <c r="H96" s="16">
-        <v>0.0045228781012</v>
+        <v>0.0048160192112</v>
       </c>
       <c r="I96" s="15" t="s">
         <v>13</v>
@@ -4721,16 +4718,16 @@
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="F97" s="14">
-        <v>7387</v>
+        <v>17743</v>
       </c>
       <c r="G97" s="15">
-        <v>271.89</v>
+        <v>345.47</v>
       </c>
       <c r="H97" s="16">
-        <v>0.0044314426196</v>
+        <v>0.0047215794225</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>13</v>
@@ -4750,16 +4747,16 @@
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="F98" s="14">
-        <v>133738</v>
+        <v>59712</v>
       </c>
       <c r="G98" s="15">
-        <v>269.88</v>
+        <v>339.34</v>
       </c>
       <c r="H98" s="16">
-        <v>0.0043986823133</v>
+        <v>0.0046377999862</v>
       </c>
       <c r="I98" s="15" t="s">
         <v>13</v>
@@ -4779,16 +4776,16 @@
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="F99" s="14">
-        <v>7666</v>
+        <v>188088</v>
       </c>
       <c r="G99" s="15">
-        <v>262.62</v>
+        <v>339.22</v>
       </c>
       <c r="H99" s="16">
-        <v>0.004280354043</v>
+        <v>0.004636159932</v>
       </c>
       <c r="I99" s="15" t="s">
         <v>13</v>
@@ -4808,16 +4805,16 @@
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="F100" s="14">
-        <v>231713</v>
+        <v>16698</v>
       </c>
       <c r="G100" s="15">
-        <v>260.72</v>
+        <v>336.70</v>
       </c>
       <c r="H100" s="16">
-        <v>0.0042493865893</v>
+        <v>0.0046017187934</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>13</v>
@@ -4837,16 +4834,16 @@
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="F101" s="14">
-        <v>12959</v>
+        <v>33629</v>
       </c>
       <c r="G101" s="15">
-        <v>260.17</v>
+        <v>335.43</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0042404223264</v>
+        <v>0.0045843615529</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>13</v>
@@ -4866,16 +4863,16 @@
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F102" s="14">
-        <v>128472</v>
+        <v>149572</v>
       </c>
       <c r="G102" s="15">
-        <v>259.65</v>
+        <v>332.81</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0042319470233</v>
+        <v>0.0045485537025</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>13</v>
@@ -4895,16 +4892,16 @@
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F103" s="14">
-        <v>992</v>
+        <v>1086</v>
       </c>
       <c r="G103" s="15">
-        <v>259.64</v>
+        <v>330.74</v>
       </c>
       <c r="H103" s="16">
-        <v>0.0042317840367</v>
+        <v>0.0045202627672</v>
       </c>
       <c r="I103" s="15" t="s">
         <v>13</v>
@@ -4924,16 +4921,16 @@
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F104" s="14">
-        <v>1789</v>
+        <v>4405</v>
       </c>
       <c r="G104" s="15">
-        <v>259.42</v>
+        <v>330.62</v>
       </c>
       <c r="H104" s="16">
-        <v>0.0042281983316</v>
+        <v>0.004518622713</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>13</v>
@@ -4953,16 +4950,16 @@
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F105" s="14">
-        <v>34469</v>
+        <v>67641</v>
       </c>
       <c r="G105" s="15">
-        <v>257.36</v>
+        <v>318.28</v>
       </c>
       <c r="H105" s="16">
-        <v>0.0041946230923</v>
+        <v>0.0043499704709</v>
       </c>
       <c r="I105" s="15" t="s">
         <v>13</v>
@@ -4982,16 +4979,16 @@
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F106" s="14">
-        <v>54292</v>
+        <v>94456</v>
       </c>
       <c r="G106" s="15">
-        <v>256.67</v>
+        <v>317.23</v>
       </c>
       <c r="H106" s="16">
-        <v>0.0041833770171</v>
+        <v>0.0043356199965</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>13</v>
@@ -5011,16 +5008,16 @@
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F107" s="14">
-        <v>1991</v>
+        <v>254871</v>
       </c>
       <c r="G107" s="15">
-        <v>256.11</v>
+        <v>310.79</v>
       </c>
       <c r="H107" s="16">
-        <v>0.0041742497676</v>
+        <v>0.0042476037535</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>13</v>
@@ -5040,16 +5037,16 @@
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="F108" s="14">
-        <v>56852</v>
+        <v>8558</v>
       </c>
       <c r="G108" s="15">
-        <v>255.92</v>
+        <v>304.09</v>
       </c>
       <c r="H108" s="16">
-        <v>0.0041711530222</v>
+        <v>0.0041560340596</v>
       </c>
       <c r="I108" s="15" t="s">
         <v>13</v>
@@ -5060,25 +5057,25 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="F109" s="14">
-        <v>21245</v>
+        <v>147120</v>
       </c>
       <c r="G109" s="15">
-        <v>252.11</v>
+        <v>304.04</v>
       </c>
       <c r="H109" s="16">
-        <v>0.0041090551283</v>
+        <v>0.0041553507037</v>
       </c>
       <c r="I109" s="15" t="s">
         <v>13</v>
@@ -5089,25 +5086,25 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C110" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="D110" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="F110" s="14">
-        <v>4634</v>
+        <v>15132</v>
       </c>
       <c r="G110" s="15">
-        <v>251.78</v>
+        <v>299.13</v>
       </c>
       <c r="H110" s="16">
-        <v>0.0041036765705</v>
+        <v>0.004088245152</v>
       </c>
       <c r="I110" s="15" t="s">
         <v>13</v>
@@ -5127,16 +5124,16 @@
         <v>13</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F111" s="14">
-        <v>3997</v>
+        <v>174242</v>
       </c>
       <c r="G111" s="15">
-        <v>250.53</v>
+        <v>296.54</v>
       </c>
       <c r="H111" s="16">
-        <v>0.0040833032457</v>
+        <v>0.0040528473151</v>
       </c>
       <c r="I111" s="15" t="s">
         <v>13</v>
@@ -5156,16 +5153,16 @@
         <v>13</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>214</v>
+        <v>53</v>
       </c>
       <c r="F112" s="14">
-        <v>16126</v>
+        <v>14409</v>
       </c>
       <c r="G112" s="15">
-        <v>247.10</v>
+        <v>292.11</v>
       </c>
       <c r="H112" s="16">
-        <v>0.0040273988425</v>
+        <v>0.0039923019802</v>
       </c>
       <c r="I112" s="15" t="s">
         <v>13</v>
@@ -5185,16 +5182,16 @@
         <v>13</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F113" s="14">
-        <v>135731</v>
+        <v>15767</v>
       </c>
       <c r="G113" s="15">
-        <v>243.49</v>
+        <v>288.65</v>
       </c>
       <c r="H113" s="16">
-        <v>0.0039685606806</v>
+        <v>0.0039450137503</v>
       </c>
       <c r="I113" s="15" t="s">
         <v>13</v>
@@ -5214,16 +5211,16 @@
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="F114" s="14">
-        <v>58953</v>
+        <v>168325</v>
       </c>
       <c r="G114" s="15">
-        <v>242.56</v>
+        <v>288.32</v>
       </c>
       <c r="H114" s="16">
-        <v>0.0039534029269</v>
+        <v>0.0039405036012</v>
       </c>
       <c r="I114" s="15" t="s">
         <v>13</v>
@@ -5243,16 +5240,16 @@
         <v>13</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F115" s="14">
-        <v>158628</v>
+        <v>3534</v>
       </c>
       <c r="G115" s="15">
-        <v>240.13</v>
+        <v>286.75</v>
       </c>
       <c r="H115" s="16">
-        <v>0.0039137971836</v>
+        <v>0.0039190462251</v>
       </c>
       <c r="I115" s="15" t="s">
         <v>13</v>
@@ -5272,16 +5269,16 @@
         <v>13</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>221</v>
+        <v>45</v>
       </c>
       <c r="F116" s="14">
-        <v>29396</v>
+        <v>8672</v>
       </c>
       <c r="G116" s="15">
-        <v>231.52</v>
+        <v>286.05</v>
       </c>
       <c r="H116" s="16">
-        <v>0.0037734657225</v>
+        <v>0.0039094792422</v>
       </c>
       <c r="I116" s="15" t="s">
         <v>13</v>
@@ -5301,16 +5298,16 @@
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F117" s="14">
-        <v>15160</v>
+        <v>8136</v>
       </c>
       <c r="G117" s="15">
-        <v>231.15</v>
+        <v>284.59</v>
       </c>
       <c r="H117" s="16">
-        <v>0.0037674352183</v>
+        <v>0.0038895252492</v>
       </c>
       <c r="I117" s="15" t="s">
         <v>13</v>
@@ -5330,16 +5327,16 @@
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="F118" s="14">
-        <v>17559</v>
+        <v>8118</v>
       </c>
       <c r="G118" s="15">
-        <v>229.14</v>
+        <v>275.05</v>
       </c>
       <c r="H118" s="16">
-        <v>0.0037346749121</v>
+        <v>0.0037591409389</v>
       </c>
       <c r="I118" s="15" t="s">
         <v>13</v>
@@ -5350,25 +5347,25 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C119" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="C119" s="13" t="s">
-        <v>275</v>
-      </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="F119" s="14">
-        <v>6318</v>
+        <v>36682</v>
       </c>
       <c r="G119" s="15">
-        <v>228.93</v>
+        <v>271.80</v>
       </c>
       <c r="H119" s="16">
-        <v>0.0037312521935</v>
+        <v>0.0037147228038</v>
       </c>
       <c r="I119" s="15" t="s">
         <v>13</v>
@@ -5379,25 +5376,25 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C120" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="13" t="s">
-        <v>277</v>
-      </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F120" s="14">
-        <v>153502</v>
+        <v>5104</v>
       </c>
       <c r="G120" s="15">
-        <v>223.30</v>
+        <v>267.94</v>
       </c>
       <c r="H120" s="16">
-        <v>0.0036394907387</v>
+        <v>0.0036619677265</v>
       </c>
       <c r="I120" s="15" t="s">
         <v>13</v>
@@ -5408,25 +5405,25 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C121" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C121" s="13" t="s">
-        <v>279</v>
-      </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="F121" s="14">
-        <v>81168</v>
+        <v>64849</v>
       </c>
       <c r="G121" s="15">
-        <v>222.28</v>
+        <v>266.92</v>
       </c>
       <c r="H121" s="16">
-        <v>0.0036228661057</v>
+        <v>0.0036480272656</v>
       </c>
       <c r="I121" s="15" t="s">
         <v>13</v>
@@ -5437,25 +5434,25 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C122" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="F122" s="14">
-        <v>37587</v>
+        <v>14127</v>
       </c>
       <c r="G122" s="15">
-        <v>221.63</v>
+        <v>265.98</v>
       </c>
       <c r="H122" s="16">
-        <v>0.0036122719768</v>
+        <v>0.0036351801742</v>
       </c>
       <c r="I122" s="15" t="s">
         <v>13</v>
@@ -5466,25 +5463,25 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C123" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C123" s="13" t="s">
-        <v>283</v>
-      </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F123" s="14">
-        <v>21077</v>
+        <v>16685</v>
       </c>
       <c r="G123" s="15">
-        <v>220.09</v>
+        <v>265.06</v>
       </c>
       <c r="H123" s="16">
-        <v>0.0035871720407</v>
+        <v>0.0036226064252</v>
       </c>
       <c r="I123" s="15" t="s">
         <v>13</v>
@@ -5495,25 +5492,25 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C124" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>285</v>
-      </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="F124" s="14">
-        <v>95691</v>
+        <v>39652</v>
       </c>
       <c r="G124" s="15">
-        <v>219.80</v>
+        <v>256.37</v>
       </c>
       <c r="H124" s="16">
-        <v>0.0035824454293</v>
+        <v>0.0035038391656</v>
       </c>
       <c r="I124" s="15" t="s">
         <v>13</v>
@@ -5524,25 +5521,25 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C125" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>287</v>
-      </c>
       <c r="D125" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="F125" s="14">
-        <v>378371</v>
+        <v>105254</v>
       </c>
       <c r="G125" s="15">
-        <v>216.88</v>
+        <v>253.91</v>
       </c>
       <c r="H125" s="16">
-        <v>0.0035348533426</v>
+        <v>0.0034702180541</v>
       </c>
       <c r="I125" s="15" t="s">
         <v>13</v>
@@ -5553,25 +5550,25 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C126" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C126" s="13" t="s">
-        <v>289</v>
-      </c>
       <c r="D126" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F126" s="14">
-        <v>8014</v>
+        <v>31156</v>
       </c>
       <c r="G126" s="15">
-        <v>215.93</v>
+        <v>252.33</v>
       </c>
       <c r="H126" s="16">
-        <v>0.0035193696158</v>
+        <v>0.0034486240069</v>
       </c>
       <c r="I126" s="15" t="s">
         <v>13</v>
@@ -5582,25 +5579,25 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C127" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="D127" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F127" s="14">
-        <v>6837</v>
+        <v>5755</v>
       </c>
       <c r="G127" s="15">
-        <v>195.39</v>
+        <v>251.36</v>
       </c>
       <c r="H127" s="16">
-        <v>0.003184595143</v>
+        <v>0.003435366902</v>
       </c>
       <c r="I127" s="15" t="s">
         <v>13</v>
@@ -5620,16 +5617,16 @@
         <v>13</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>46</v>
+        <v>291</v>
       </c>
       <c r="F128" s="14">
-        <v>14327</v>
+        <v>32337</v>
       </c>
       <c r="G128" s="15">
-        <v>194.12</v>
+        <v>250.16</v>
       </c>
       <c r="H128" s="16">
-        <v>0.003163895845</v>
+        <v>0.0034189663598</v>
       </c>
       <c r="I128" s="15" t="s">
         <v>13</v>
@@ -5649,16 +5646,16 @@
         <v>13</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F129" s="14">
-        <v>33209</v>
+        <v>141313</v>
       </c>
       <c r="G129" s="15">
-        <v>193.87</v>
+        <v>246.92</v>
       </c>
       <c r="H129" s="16">
-        <v>0.0031598211801</v>
+        <v>0.0033746848959</v>
       </c>
       <c r="I129" s="15" t="s">
         <v>13</v>
@@ -5678,16 +5675,16 @@
         <v>13</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F130" s="14">
-        <v>41927</v>
+        <v>41346</v>
       </c>
       <c r="G130" s="15">
-        <v>181.65</v>
+        <v>241.54</v>
       </c>
       <c r="H130" s="16">
-        <v>0.002960651557</v>
+        <v>0.0033011557985</v>
       </c>
       <c r="I130" s="15" t="s">
         <v>13</v>
@@ -5707,16 +5704,16 @@
         <v>13</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="F131" s="14">
-        <v>323367</v>
+        <v>21051</v>
       </c>
       <c r="G131" s="15">
-        <v>181.51</v>
+        <v>237.14</v>
       </c>
       <c r="H131" s="16">
-        <v>0.0029583697447</v>
+        <v>0.0032410204772</v>
       </c>
       <c r="I131" s="15" t="s">
         <v>13</v>
@@ -5736,16 +5733,16 @@
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F132" s="14">
-        <v>4424</v>
+        <v>6950</v>
       </c>
       <c r="G132" s="15">
-        <v>178.90</v>
+        <v>230.86</v>
       </c>
       <c r="H132" s="16">
-        <v>0.0029158302425</v>
+        <v>0.0031551909731</v>
       </c>
       <c r="I132" s="15" t="s">
         <v>13</v>
@@ -5765,16 +5762,16 @@
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="F133" s="14">
-        <v>19137</v>
+        <v>47309</v>
       </c>
       <c r="G133" s="15">
-        <v>178.36</v>
+        <v>225.97</v>
       </c>
       <c r="H133" s="16">
-        <v>0.0029070289662</v>
+        <v>0.0030883587637</v>
       </c>
       <c r="I133" s="15" t="s">
         <v>13</v>
@@ -5794,16 +5791,16 @@
         <v>13</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="F134" s="14">
-        <v>55625</v>
+        <v>8820</v>
       </c>
       <c r="G134" s="15">
-        <v>172.66</v>
+        <v>221.45</v>
       </c>
       <c r="H134" s="16">
-        <v>0.0028141266052</v>
+        <v>0.0030265833882</v>
       </c>
       <c r="I134" s="15" t="s">
         <v>13</v>
@@ -5823,16 +5820,16 @@
         <v>13</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="F135" s="14">
-        <v>8803</v>
+        <v>416111</v>
       </c>
       <c r="G135" s="15">
-        <v>169.67</v>
+        <v>213.34</v>
       </c>
       <c r="H135" s="16">
-        <v>0.0027653936123</v>
+        <v>0.0029157430573</v>
       </c>
       <c r="I135" s="15" t="s">
         <v>13</v>
@@ -5852,16 +5849,16 @@
         <v>13</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>214</v>
+        <v>23</v>
       </c>
       <c r="F136" s="14">
-        <v>411</v>
+        <v>17452</v>
       </c>
       <c r="G136" s="15">
-        <v>166.34</v>
+        <v>207.36</v>
       </c>
       <c r="H136" s="16">
-        <v>0.0027111190751</v>
+        <v>0.0028340136887</v>
       </c>
       <c r="I136" s="15" t="s">
         <v>13</v>
@@ -5881,16 +5878,16 @@
         <v>13</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="F137" s="14">
-        <v>15839</v>
+        <v>355679</v>
       </c>
       <c r="G137" s="15">
-        <v>164.66</v>
+        <v>205.87</v>
       </c>
       <c r="H137" s="16">
-        <v>0.0026837373266</v>
+        <v>0.0028136496822</v>
       </c>
       <c r="I137" s="15" t="s">
         <v>13</v>
@@ -5910,16 +5907,16 @@
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>314</v>
+        <v>123</v>
       </c>
       <c r="F138" s="14">
-        <v>537</v>
+        <v>156646</v>
       </c>
       <c r="G138" s="15">
-        <v>160.52</v>
+        <v>195.27</v>
       </c>
       <c r="H138" s="16">
-        <v>0.002616260875</v>
+        <v>0.0026687782263</v>
       </c>
       <c r="I138" s="15" t="s">
         <v>13</v>
@@ -5930,25 +5927,25 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C139" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="C139" s="13" t="s">
-        <v>316</v>
-      </c>
       <c r="D139" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="F139" s="14">
-        <v>32877</v>
+        <v>69156</v>
       </c>
       <c r="G139" s="15">
-        <v>159.78</v>
+        <v>190.18</v>
       </c>
       <c r="H139" s="16">
-        <v>0.0026041998667</v>
+        <v>0.0025992125932</v>
       </c>
       <c r="I139" s="15" t="s">
         <v>13</v>
@@ -5959,25 +5956,25 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C140" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="C140" s="13" t="s">
-        <v>318</v>
-      </c>
       <c r="D140" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F140" s="14">
-        <v>7881</v>
+        <v>2716</v>
       </c>
       <c r="G140" s="15">
-        <v>155.82</v>
+        <v>182.77</v>
       </c>
       <c r="H140" s="16">
-        <v>0.0025396571738</v>
+        <v>0.0024979392452</v>
       </c>
       <c r="I140" s="15" t="s">
         <v>13</v>
@@ -5988,25 +5985,25 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C141" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="C141" s="13" t="s">
-        <v>320</v>
-      </c>
       <c r="D141" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F141" s="14">
-        <v>300008</v>
+        <v>7388</v>
       </c>
       <c r="G141" s="15">
-        <v>153.87</v>
+        <v>179.66</v>
       </c>
       <c r="H141" s="16">
-        <v>0.0025078747871</v>
+        <v>0.0024554345067</v>
       </c>
       <c r="I141" s="15" t="s">
         <v>13</v>
@@ -6017,25 +6014,25 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="C142" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="C142" s="13" t="s">
-        <v>322</v>
-      </c>
       <c r="D142" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="F142" s="14">
-        <v>2510</v>
+        <v>329983</v>
       </c>
       <c r="G142" s="15">
-        <v>151.24</v>
+        <v>178.12</v>
       </c>
       <c r="H142" s="16">
-        <v>0.0024650093118</v>
+        <v>0.0024343871443</v>
       </c>
       <c r="I142" s="15" t="s">
         <v>13</v>
@@ -6046,25 +6043,25 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C143" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="C143" s="13" t="s">
-        <v>324</v>
-      </c>
       <c r="D143" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="F143" s="14">
-        <v>51550</v>
+        <v>452</v>
       </c>
       <c r="G143" s="15">
-        <v>141.76</v>
+        <v>174.16</v>
       </c>
       <c r="H143" s="16">
-        <v>0.0023104980166</v>
+        <v>0.0023802653551</v>
       </c>
       <c r="I143" s="15" t="s">
         <v>13</v>
@@ -6075,25 +6072,25 @@
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
       <c r="B144" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C144" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="C144" s="13" t="s">
-        <v>326</v>
-      </c>
       <c r="D144" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F144" s="14">
-        <v>62200</v>
+        <v>156269</v>
       </c>
       <c r="G144" s="15">
-        <v>138.03</v>
+        <v>173.86</v>
       </c>
       <c r="H144" s="16">
-        <v>0.0022497040155</v>
+        <v>0.0023761652195</v>
       </c>
       <c r="I144" s="15" t="s">
         <v>13</v>
@@ -6104,25 +6101,25 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="C145" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="D145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="F145" s="14">
-        <v>6708</v>
+        <v>582</v>
       </c>
       <c r="G145" s="15">
-        <v>133.45</v>
+        <v>170.38</v>
       </c>
       <c r="H145" s="16">
-        <v>0.0021750561535</v>
+        <v>0.0023286036472</v>
       </c>
       <c r="I145" s="15" t="s">
         <v>13</v>
@@ -6142,16 +6139,16 @@
         <v>13</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F146" s="14">
-        <v>136393</v>
+        <v>97812</v>
       </c>
       <c r="G146" s="15">
-        <v>133</v>
+        <v>167.21</v>
       </c>
       <c r="H146" s="16">
-        <v>0.0021677217566</v>
+        <v>0.0022852788816</v>
       </c>
       <c r="I146" s="15" t="s">
         <v>13</v>
@@ -6171,16 +6168,16 @@
         <v>13</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="F147" s="14">
-        <v>1152</v>
+        <v>36150</v>
       </c>
       <c r="G147" s="15">
-        <v>127.11</v>
+        <v>166.31</v>
       </c>
       <c r="H147" s="16">
-        <v>0.0020717226502</v>
+        <v>0.002272978475</v>
       </c>
       <c r="I147" s="15" t="s">
         <v>13</v>
@@ -6200,16 +6197,16 @@
         <v>13</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F148" s="14">
-        <v>2414</v>
+        <v>56964</v>
       </c>
       <c r="G148" s="15">
-        <v>123.50</v>
+        <v>165.68</v>
       </c>
       <c r="H148" s="16">
-        <v>0.0020128844883</v>
+        <v>0.0022643681903</v>
       </c>
       <c r="I148" s="15" t="s">
         <v>13</v>
@@ -6229,16 +6226,16 @@
         <v>13</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F149" s="14">
-        <v>11864</v>
+        <v>68422</v>
       </c>
       <c r="G149" s="15">
-        <v>109.26</v>
+        <v>165.39</v>
       </c>
       <c r="H149" s="16">
-        <v>0.0017807915724</v>
+        <v>0.002260404726</v>
       </c>
       <c r="I149" s="15" t="s">
         <v>13</v>
@@ -6258,16 +6255,16 @@
         <v>13</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="F150" s="14">
-        <v>12157</v>
+        <v>5521</v>
       </c>
       <c r="G150" s="15">
-        <v>108.26</v>
+        <v>164.47</v>
       </c>
       <c r="H150" s="16">
-        <v>0.0017644929125</v>
+        <v>0.002247830977</v>
       </c>
       <c r="I150" s="15" t="s">
         <v>13</v>
@@ -6287,16 +6284,16 @@
         <v>13</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F151" s="14">
-        <v>16189</v>
+        <v>12993</v>
       </c>
       <c r="G151" s="15">
-        <v>100.19</v>
+        <v>153.93</v>
       </c>
       <c r="H151" s="16">
-        <v>0.0016329627277</v>
+        <v>0.0021037795481</v>
       </c>
       <c r="I151" s="15" t="s">
         <v>13</v>
@@ -6307,25 +6304,25 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
       <c r="B152" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C152" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="C152" s="13" t="s">
-        <v>343</v>
-      </c>
       <c r="D152" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F152" s="14">
-        <v>107058</v>
+        <v>13819</v>
       </c>
       <c r="G152" s="15">
-        <v>86.85</v>
+        <v>146.7</v>
       </c>
       <c r="H152" s="16">
-        <v>0.0014155386057</v>
+        <v>0.0020049662815</v>
       </c>
       <c r="I152" s="15" t="s">
         <v>13</v>
@@ -6336,25 +6333,25 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C153" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="C153" s="13" t="s">
-        <v>345</v>
-      </c>
       <c r="D153" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="F153" s="14">
-        <v>7062</v>
+        <v>150022</v>
       </c>
       <c r="G153" s="15">
-        <v>83.67</v>
+        <v>144.47</v>
       </c>
       <c r="H153" s="16">
-        <v>0.0013637088675</v>
+        <v>0.0019744886073</v>
       </c>
       <c r="I153" s="15" t="s">
         <v>13</v>
@@ -6365,25 +6362,25 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C154" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="C154" s="13" t="s">
+      <c r="D154" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="F154" s="14">
-        <v>45880</v>
+        <v>20710</v>
       </c>
       <c r="G154" s="15">
-        <v>83.43</v>
+        <v>130.40</v>
       </c>
       <c r="H154" s="16">
-        <v>0.0013597971891</v>
+        <v>0.0017821922502</v>
       </c>
       <c r="I154" s="15" t="s">
         <v>13</v>
@@ -6403,16 +6400,16 @@
         <v>13</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="F155" s="14">
-        <v>30130</v>
+        <v>187113</v>
       </c>
       <c r="G155" s="15">
-        <v>80.34</v>
+        <v>95.35</v>
       </c>
       <c r="H155" s="16">
-        <v>0.0013094343302</v>
+        <v>0.0013031597474</v>
       </c>
       <c r="I155" s="15" t="s">
         <v>13</v>
@@ -6423,25 +6420,25 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F156" s="14">
-        <v>130801</v>
+        <v>50472</v>
       </c>
       <c r="G156" s="15">
-        <v>66.71</v>
+        <v>94.11</v>
       </c>
       <c r="H156" s="16">
-        <v>0.0010872835968</v>
+        <v>0.0012862125204</v>
       </c>
       <c r="I156" s="15" t="s">
         <v>13</v>
@@ -6452,25 +6449,25 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D157" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="F157" s="14">
-        <v>34931</v>
+        <v>98439</v>
       </c>
       <c r="G157" s="15">
-        <v>45.24</v>
+        <v>84.51</v>
       </c>
       <c r="H157" s="16">
-        <v>0.0007373513704</v>
+        <v>0.001155008183</v>
       </c>
       <c r="I157" s="15" t="s">
         <v>13</v>
@@ -6481,6 +6478,27 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
       <c r="B158" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F158" s="14">
+        <v>37432</v>
+      </c>
+      <c r="G158" s="15">
+        <v>53.92</v>
+      </c>
+      <c r="H158" s="16">
+        <v>0.0007369310286</v>
+      </c>
+      <c r="I158" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J158" s="11" t="s">
@@ -6488,28 +6506,7 @@
       </c>
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
-      <c r="B159" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I159" s="9" t="s">
+      <c r="B159" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J159" s="11" t="s">
@@ -6517,7 +6514,28 @@
       </c>
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I160" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J160" s="11" t="s">
@@ -6525,28 +6543,7 @@
       </c>
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
-      <c r="B161" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I161" s="9" t="s">
+      <c r="B161" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J161" s="11" t="s">
@@ -6554,7 +6551,28 @@
       </c>
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I162" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J162" s="11" t="s">
@@ -6562,36 +6580,36 @@
       </c>
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1">
+      <c r="B164" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I163" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J163" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" ht="15" customHeight="1">
-      <c r="B164" s="12" t="s">
+      <c r="C164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H164" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I164" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J164" s="11" t="s">
@@ -6599,28 +6617,7 @@
       </c>
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1">
-      <c r="B165" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I165" s="9" t="s">
+      <c r="B165" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J165" s="11" t="s">
@@ -6628,7 +6625,28 @@
       </c>
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1">
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I166" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J166" s="11" t="s">
@@ -6636,36 +6654,36 @@
       </c>
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1">
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1">
+      <c r="B168" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="C167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I167" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J167" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" ht="15" customHeight="1">
-      <c r="B168" s="12" t="s">
+      <c r="H168" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I168" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J168" s="11" t="s">
@@ -6673,28 +6691,7 @@
       </c>
     </row>
     <row r="169" spans="2:10" ht="15" customHeight="1">
-      <c r="B169" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I169" s="9" t="s">
+      <c r="B169" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J169" s="11" t="s">
@@ -6702,7 +6699,28 @@
       </c>
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1">
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I170" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J170" s="11" t="s">
@@ -6710,28 +6728,7 @@
       </c>
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1">
-      <c r="B171" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I171" s="9" t="s">
+      <c r="B171" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J171" s="11" t="s">
@@ -6739,7 +6736,28 @@
       </c>
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1">
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I172" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J172" s="11" t="s">
@@ -6747,28 +6765,7 @@
       </c>
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1">
-      <c r="B173" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E173" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G173" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I173" s="9" t="s">
+      <c r="B173" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J173" s="11" t="s">
@@ -6776,7 +6773,28 @@
       </c>
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1">
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I174" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J174" s="11" t="s">
@@ -6784,28 +6802,7 @@
       </c>
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1">
-      <c r="B175" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I175" s="9" t="s">
+      <c r="B175" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J175" s="11" t="s">
@@ -6813,7 +6810,28 @@
       </c>
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1">
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I176" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J176" s="11" t="s">
@@ -6821,28 +6839,7 @@
       </c>
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1">
-      <c r="B177" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I177" s="9" t="s">
+      <c r="B177" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J177" s="11" t="s">
@@ -6850,7 +6847,28 @@
       </c>
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1">
-      <c r="B178" s="12" t="s">
+      <c r="B178" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H178" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I178" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J178" s="11" t="s">
@@ -6858,28 +6876,7 @@
       </c>
     </row>
     <row r="179" spans="2:10" ht="15" customHeight="1">
-      <c r="B179" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G179" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I179" s="9" t="s">
+      <c r="B179" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J179" s="11" t="s">
@@ -6887,7 +6884,28 @@
       </c>
     </row>
     <row r="180" spans="2:10" ht="15" customHeight="1">
-      <c r="B180" s="12" t="s">
+      <c r="B180" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I180" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J180" s="11" t="s">
@@ -6895,28 +6913,7 @@
       </c>
     </row>
     <row r="181" spans="2:10" ht="15" customHeight="1">
-      <c r="B181" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D181" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G181" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H181" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I181" s="9" t="s">
+      <c r="B181" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J181" s="11" t="s">
@@ -6924,7 +6921,28 @@
       </c>
     </row>
     <row r="182" spans="2:10" ht="15" customHeight="1">
-      <c r="B182" s="12" t="s">
+      <c r="B182" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I182" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J182" s="11" t="s">
@@ -6932,28 +6950,7 @@
       </c>
     </row>
     <row r="183" spans="2:10" ht="15" customHeight="1">
-      <c r="B183" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D183" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E183" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F183" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I183" s="9" t="s">
+      <c r="B183" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J183" s="11" t="s">
@@ -6961,7 +6958,28 @@
       </c>
     </row>
     <row r="184" spans="2:10" ht="15" customHeight="1">
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H184" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I184" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J184" s="11" t="s">
@@ -6969,28 +6987,7 @@
       </c>
     </row>
     <row r="185" spans="2:10" ht="15" customHeight="1">
-      <c r="B185" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D185" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G185" s="9">
-        <v>265.85</v>
-      </c>
-      <c r="H185" s="10">
-        <v>0.0043329987142</v>
-      </c>
-      <c r="I185" s="9" t="s">
+      <c r="B185" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J185" s="11" t="s">
@@ -6998,7 +6995,28 @@
       </c>
     </row>
     <row r="186" spans="2:10" ht="15" customHeight="1">
-      <c r="B186" s="12" t="s">
+      <c r="B186" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="9">
+        <v>199.66</v>
+      </c>
+      <c r="H186" s="10">
+        <v>0.0027287768764</v>
+      </c>
+      <c r="I186" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J186" s="11" t="s">
@@ -7006,37 +7024,16 @@
       </c>
     </row>
     <row r="187" spans="2:10" ht="15" customHeight="1">
-      <c r="B187" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="C187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="18">
-        <v>-215.12220077999518</v>
-      </c>
-      <c r="H187" s="19">
-        <v>-0.0035062035711727877</v>
-      </c>
-      <c r="I187" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J187" s="20" t="s">
+      <c r="B187" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J187" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="188" spans="2:10" ht="15" customHeight="1">
       <c r="B188" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C188" s="18" t="s">
         <v>13</v>
@@ -7051,10 +7048,10 @@
         <v>13</v>
       </c>
       <c r="G188" s="18">
-        <v>61354.73779922</v>
+        <v>-104.23722099997394</v>
       </c>
       <c r="H188" s="19">
-        <v>0.999999999991827</v>
+        <v>-0.001424622449813972</v>
       </c>
       <c r="I188" s="18" t="s">
         <v>13</v>
@@ -7063,136 +7060,152 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="2:3" ht="15" customHeight="1">
-      <c r="B190" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="C190" s="22"/>
+    <row r="189" spans="2:10" ht="15" customHeight="1">
+      <c r="B189" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="18">
+        <v>73168.312779</v>
+      </c>
+      <c r="H189" s="19">
+        <v>0.9999999999922853</v>
+      </c>
+      <c r="I189" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J189" s="20" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="191" spans="2:3" ht="15" customHeight="1">
-      <c r="B191" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="C191" s="24" t="s">
+      <c r="B191" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C191" s="22"/>
+    </row>
+    <row r="192" spans="2:3" ht="15" customHeight="1">
+      <c r="B192" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="C192" s="24" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="192" spans="2:3" ht="15" customHeight="1">
-      <c r="B192" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C192" s="26">
-        <v>54000</v>
       </c>
     </row>
     <row r="193" spans="2:3" ht="15" customHeight="1">
       <c r="B193" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C193" s="26">
-        <v>1400</v>
+        <v>375</v>
+      </c>
+      <c r="C193" s="25">
+        <v>84000</v>
       </c>
     </row>
     <row r="194" spans="2:3" ht="15" customHeight="1">
       <c r="B194" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="C194" s="26">
-        <v>2300</v>
+        <v>294</v>
+      </c>
+      <c r="C194" s="25">
+        <v>26000</v>
       </c>
     </row>
     <row r="195" spans="2:3" ht="15" customHeight="1">
       <c r="B195" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="C195" s="26">
-        <v>4500</v>
+        <v>252</v>
+      </c>
+      <c r="C195" s="25">
+        <v>11350</v>
       </c>
     </row>
     <row r="196" spans="2:3" ht="15" customHeight="1">
       <c r="B196" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C196" s="26">
-        <v>250</v>
+        <v>376</v>
+      </c>
+      <c r="C196" s="25">
+        <v>35000</v>
       </c>
     </row>
     <row r="197" spans="2:3" ht="15" customHeight="1">
       <c r="B197" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C197" s="26">
-        <v>11000</v>
+        <v>292</v>
+      </c>
+      <c r="C197" s="25">
+        <v>3000</v>
       </c>
     </row>
     <row r="199" spans="2:9" ht="15" customHeight="1">
       <c r="B199" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C199" s="27"/>
-      <c r="D199" s="27"/>
-      <c r="E199" s="27"/>
-      <c r="F199" s="27"/>
-      <c r="G199" s="27"/>
-      <c r="H199" s="27"/>
-      <c r="I199" s="27"/>
+        <v>377</v>
+      </c>
+      <c r="C199" s="26"/>
+      <c r="D199" s="26"/>
+      <c r="E199" s="26"/>
+      <c r="F199" s="26"/>
+      <c r="G199" s="26"/>
+      <c r="H199" s="26"/>
+      <c r="I199" s="26"/>
     </row>
     <row r="200" spans="2:8" ht="15" customHeight="1">
       <c r="B200" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C200" s="27"/>
-      <c r="D200" s="27"/>
-      <c r="E200" s="27"/>
-      <c r="F200" s="27"/>
-      <c r="G200" s="27"/>
-      <c r="H200" s="27"/>
+        <v>378</v>
+      </c>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="26"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="26"/>
+      <c r="H200" s="26"/>
     </row>
     <row r="201" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B201" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C201" s="27"/>
-      <c r="D201" s="27"/>
-      <c r="E201" s="27"/>
-      <c r="F201" s="27"/>
-      <c r="G201" s="27"/>
-      <c r="H201" s="27"/>
+      <c r="B201" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C201" s="26"/>
+      <c r="D201" s="26"/>
+      <c r="E201" s="26"/>
+      <c r="F201" s="26"/>
+      <c r="G201" s="26"/>
+      <c r="H201" s="26"/>
     </row>
     <row r="202" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B202" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="C202" s="27"/>
-      <c r="D202" s="27"/>
-      <c r="E202" s="27"/>
-      <c r="F202" s="27"/>
-      <c r="G202" s="27"/>
-      <c r="H202" s="27"/>
+      <c r="B202" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="C202" s="26"/>
+      <c r="D202" s="26"/>
+      <c r="E202" s="26"/>
+      <c r="F202" s="26"/>
+      <c r="G202" s="26"/>
+      <c r="H202" s="26"/>
     </row>
     <row r="203" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B203" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="C203" s="27"/>
-      <c r="D203" s="27"/>
-      <c r="E203" s="27"/>
-      <c r="F203" s="27"/>
-      <c r="G203" s="27"/>
-      <c r="H203" s="27"/>
+      <c r="B203" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="C203" s="26"/>
+      <c r="D203" s="26"/>
+      <c r="E203" s="26"/>
+      <c r="F203" s="26"/>
+      <c r="G203" s="26"/>
+      <c r="H203" s="26"/>
     </row>
     <row r="206" ht="15">
-      <c r="B206" s="27" t="s">
-        <v>381</v>
+      <c r="B206" s="26" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="221" ht="15">
-      <c r="B221" s="27" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="222" ht="15">
-      <c r="B222" s="27" t="s">
+      <c r="B221" s="26" t="s">
         <v>383</v>
       </c>
     </row>
